--- a/automation/reports/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/Excel/Automation_Test_Report.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.001</v>
+        <v>25.774</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.224</v>
+        <v>0.236</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.189</v>
+        <v>0.288</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.239</v>
+        <v>0.218</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.182</v>
+        <v>0.31</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.369</v>
+        <v>0.242</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.275</v>
+        <v>0.332</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.317</v>
+        <v>0.258</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.374</v>
+        <v>0.445</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.315</v>
+        <v>0.506</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.181</v>
+        <v>0.308</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.217</v>
+        <v>0.29</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.203</v>
+        <v>0.295</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.21</v>
+        <v>0.279</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.168</v>
+        <v>0.228</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.178</v>
+        <v>0.249</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.227</v>
+        <v>0.248</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.167</v>
+        <v>0.262</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.22</v>
+        <v>0.239</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.172</v>
+        <v>0.218</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.213</v>
+        <v>0.26</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.169</v>
+        <v>0.229</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.207</v>
+        <v>0.216</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.166</v>
+        <v>0.27</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.212</v>
+        <v>0.24</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.175</v>
+        <v>0.224</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.18</v>
+        <v>0.243</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.207</v>
+        <v>0.224</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.177</v>
+        <v>0.276</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.213</v>
+        <v>0.243</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.239</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.221</v>
+        <v>0.266</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.172</v>
+        <v>0.245</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.217</v>
+        <v>0.248</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.174</v>
+        <v>0.328</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.215</v>
+        <v>0.293</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.168</v>
+        <v>0.239</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.214</v>
+        <v>0.253</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3.46</v>
+        <v>14.577</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.258</v>
+        <v>0.325</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.378</v>
+        <v>0.577</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.222</v>
+        <v>0.349</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.276</v>
+        <v>0.337</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.224</v>
+        <v>0.269</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.253</v>
+        <v>0.258</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.211</v>
+        <v>0.231</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.255</v>
+        <v>0.278</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.209</v>
+        <v>0.266</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.246</v>
+        <v>0.307</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.222</v>
+        <v>0.292</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.253</v>
+        <v>0.297</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.225</v>
+        <v>0.303</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.216</v>
+        <v>0.27</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.255</v>
+        <v>0.218</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.216</v>
+        <v>0.265</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.252</v>
+        <v>0.259</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.226</v>
+        <v>0.312</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.289</v>
+        <v>0.268</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.292</v>
+        <v>0.25</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.227</v>
+        <v>0.287</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.21</v>
+        <v>0.276</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.251</v>
+        <v>0.254</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.216</v>
+        <v>0.291</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.266</v>
+        <v>0.271</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.211</v>
+        <v>0.266</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.257</v>
+        <v>0.303</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.229</v>
+        <v>0.277</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.25</v>
+        <v>0.218</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.215</v>
+        <v>0.294</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.248</v>
+        <v>0.282</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.22</v>
+        <v>0.252</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.258</v>
+        <v>0.297</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.214</v>
+        <v>0.285</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.254</v>
+        <v>0.248</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.212</v>
+        <v>0.261</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.256</v>
+        <v>0.276</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.211</v>
+        <v>0.263</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>3.378</v>
+        <v>5.068</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.36</v>
+        <v>0.437</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.373</v>
+        <v>0.421</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.34</v>
+        <v>0.442</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.288</v>
+        <v>0.274</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.23</v>
+        <v>0.255</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.251</v>
+        <v>0.37</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.21</v>
+        <v>0.257</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.257</v>
+        <v>0.43</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.214</v>
+        <v>0.331</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.265</v>
+        <v>0.323</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.206</v>
+        <v>0.31</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.253</v>
+        <v>0.316</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>0.219</v>
+        <v>0.302</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.249</v>
+        <v>0.296</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0.21</v>
+        <v>0.294</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.215</v>
+        <v>0.303</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.242</v>
+        <v>0.292</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.209</v>
+        <v>0.301</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.242</v>
+        <v>0.311</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.21</v>
+        <v>0.304</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.247</v>
+        <v>0.328</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.216</v>
+        <v>0.293</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.249</v>
+        <v>0.268</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.208</v>
+        <v>0.303</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.198</v>
+        <v>0.274</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.275</v>
+        <v>0.292</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.226</v>
+        <v>0.534</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.261</v>
+        <v>0.305</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>5.556</v>
+        <v>4.609</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.294</v>
+        <v>0.382</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.251</v>
+        <v>0.648</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.242</v>
+        <v>0.466</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.112</v>
+        <v>0.331</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.262</v>
+        <v>0.242</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.271</v>
+        <v>0.232</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.216</v>
+        <v>0.34</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.252</v>
+        <v>0.336</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.219</v>
+        <v>0.32</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.26</v>
+        <v>0.375</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.216</v>
+        <v>0.401</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.248</v>
+        <v>0.284</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.218</v>
+        <v>0.43</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.216</v>
+        <v>0.362</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.26</v>
+        <v>0.232</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.214</v>
+        <v>0.334</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.243</v>
+        <v>0.328</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.213</v>
+        <v>0.315</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.255</v>
+        <v>0.382</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.212</v>
+        <v>0.322</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.254</v>
+        <v>0.285</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.223</v>
+        <v>0.256</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.255</v>
+        <v>0.295</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.222</v>
+        <v>0.279</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.29</v>
+        <v>0.256</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.211</v>
+        <v>0.298</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.262</v>
+        <v>0.275</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.208</v>
+        <v>0.258</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.263</v>
+        <v>0.314</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.216</v>
+        <v>0.296</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.281</v>
+        <v>0.274</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.219</v>
+        <v>0.304</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.321</v>
+        <v>0.277</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.248</v>
+        <v>0.252</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.222</v>
+        <v>0.299</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.224</v>
+        <v>0.272</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.252</v>
+        <v>0.26</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.22</v>
+        <v>0.303</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.262</v>
+        <v>0.273</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.24</v>
+        <v>0.257</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.261</v>
+        <v>0.308</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.212</v>
+        <v>0.28</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.267</v>
+        <v>0.265</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>0.217</v>
+        <v>0.308</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.252</v>
+        <v>0.28</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.219</v>
+        <v>0.275</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.249</v>
+        <v>0.318</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.233</v>
+        <v>0.274</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.265</v>
+        <v>0.276</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>10.929</v>
+        <v>4.643</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.298</v>
+        <v>0.336</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.325</v>
+        <v>0.312</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.219</v>
+        <v>0.301</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>0.261</v>
+        <v>0.31</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>0.217</v>
+        <v>0.282</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.26</v>
+        <v>0.227</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.224</v>
+        <v>0.282</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.266</v>
+        <v>0.326</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.195</v>
+        <v>0.278</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.258</v>
+        <v>0.306</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.214</v>
+        <v>0.251</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.267</v>
+        <v>0.304</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.196</v>
+        <v>0.266</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.245</v>
+        <v>0.318</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.211</v>
+        <v>0.257</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.267</v>
+        <v>0.307</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.224</v>
+        <v>0.254</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.288</v>
+        <v>0.307</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.222</v>
+        <v>0.252</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.284</v>
+        <v>0.305</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.217</v>
+        <v>0.266</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.26</v>
+        <v>0.304</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.225</v>
+        <v>0.267</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.272</v>
+        <v>0.299</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.223</v>
+        <v>0.25</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.292</v>
+        <v>0.317</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.256</v>
+        <v>0.252</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.244</v>
+        <v>0.304</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.211</v>
+        <v>0.251</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.269</v>
+        <v>0.352</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.229</v>
+        <v>0.259</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.263</v>
+        <v>0.304</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.22</v>
+        <v>0.248</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.268</v>
+        <v>0.299</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.216</v>
+        <v>0.248</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.244</v>
+        <v>0.3</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.217</v>
+        <v>0.234</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.257</v>
+        <v>0.311</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.217</v>
+        <v>0.265</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.286</v>
+        <v>0.305</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.224</v>
+        <v>0.266</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.273</v>
+        <v>0.299</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.22</v>
+        <v>0.246</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.249</v>
+        <v>0.309</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>0.22</v>
+        <v>0.246</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.258</v>
+        <v>0.3</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.219</v>
+        <v>0.278</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.31</v>
+        <v>0.308</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>3.164</v>
+        <v>3.579</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.265</v>
+        <v>0.293</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>0.25</v>
+        <v>0.303</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>0.221</v>
+        <v>0.287</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0.267</v>
+        <v>0.331</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0.234</v>
+        <v>0.267</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>0.117</v>
+        <v>0.257</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0.316</v>
+        <v>0.337</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>0.259</v>
+        <v>0.214</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0.227</v>
+        <v>0.302</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>0.29</v>
+        <v>0.293</v>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>0.224</v>
+        <v>0.311</v>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.233</v>
+        <v>0.319</v>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0.251</v>
+        <v>0.268</v>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>0.215</v>
+        <v>0.314</v>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.239</v>
+        <v>0.306</v>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>0.251</v>
+        <v>0.32</v>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>0.234</v>
+        <v>0.325</v>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.267</v>
+        <v>0.291</v>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>0.22</v>
+        <v>0.301</v>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0.237</v>
+        <v>0.335</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>0.215</v>
+        <v>0.318</v>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.261</v>
+        <v>0.309</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>0.222</v>
+        <v>0.322</v>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.277</v>
+        <v>0.322</v>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>0.22</v>
+        <v>0.303</v>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.133</v>
+        <v>0.369</v>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.363</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.253</v>
+        <v>0.294</v>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.226</v>
+        <v>0.292</v>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="E243" s="2" t="n">
-        <v>0.126</v>
+        <v>0.285</v>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>0.285</v>
+        <v>0.284</v>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="E245" s="2" t="n">
-        <v>0.26</v>
+        <v>0.291</v>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.235</v>
+        <v>0.292</v>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>0.249</v>
+        <v>0.284</v>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.213</v>
+        <v>0.282</v>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         </is>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.2</v>
+        <v>0.283</v>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.246</v>
+        <v>0.305</v>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="E252" s="2" t="n">
-        <v>0.216</v>
+        <v>0.296</v>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="E253" s="2" t="n">
-        <v>0.281</v>
+        <v>0.286</v>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0.255</v>
+        <v>0.228</v>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="E255" s="2" t="n">
-        <v>0.257</v>
+        <v>0.313</v>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.246</v>
+        <v>0.257</v>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>0.256</v>
+        <v>0.307</v>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.227</v>
+        <v>0.293</v>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.198</v>
+        <v>0.257</v>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.233</v>
+        <v>0.299</v>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.226</v>
+        <v>0.282</v>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="E262" s="2" t="n">
-        <v>3.259</v>
+        <v>2.493</v>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.268</v>
+        <v>0.303</v>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0.307</v>
+        <v>0.291</v>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0.216</v>
+        <v>0.314</v>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0.263</v>
+        <v>0.266</v>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0.222</v>
+        <v>0.284</v>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0.286</v>
+        <v>0.424</v>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.229</v>
+        <v>0.25</v>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.269</v>
+        <v>0.376</v>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.224</v>
+        <v>0.274</v>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.257</v>
+        <v>0.364</v>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.219</v>
+        <v>0.317</v>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.222</v>
+        <v>0.297</v>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.28</v>
+        <v>0.272</v>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>0.219</v>
+        <v>0.25</v>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0.29</v>
+        <v>0.292</v>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>0.222</v>
+        <v>0.272</v>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.251</v>
+        <v>0.249</v>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.217</v>
+        <v>0.313</v>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>0.255</v>
+        <v>0.275</v>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>0.218</v>
+        <v>0.248</v>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>0.271</v>
+        <v>0.298</v>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.201</v>
+        <v>0.334</v>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>0.263</v>
+        <v>0.309</v>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.219</v>
+        <v>0.316</v>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>0.199</v>
+        <v>0.293</v>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>0.252</v>
+        <v>0.269</v>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>0.217</v>
+        <v>0.3</v>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>0.217</v>
+        <v>0.274</v>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>0.26</v>
+        <v>0.255</v>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.213</v>
+        <v>0.342</v>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>0.263</v>
+        <v>0.305</v>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="E295" s="2" t="n">
-        <v>0.223</v>
+        <v>0.3</v>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>0.288</v>
+        <v>0.303</v>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>0.282</v>
+        <v>0.296</v>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>0.238</v>
+        <v>0.307</v>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>0.215</v>
+        <v>0.298</v>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.258</v>
+        <v>0.318</v>
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.195</v>
+        <v>0.265</v>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>1.322</v>
+        <v>2.101</v>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0.261</v>
+        <v>0.294</v>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0.277</v>
+        <v>0.308</v>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="E305" s="2" t="n">
-        <v>0.217</v>
+        <v>0.268</v>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>0.257</v>
+        <v>0.254</v>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.198</v>
+        <v>0.293</v>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0.26</v>
+        <v>0.291</v>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         </is>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0.285</v>
+        <v>0.289</v>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0.242</v>
+        <v>0.275</v>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>0.24</v>
+        <v>0.254</v>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>0.27</v>
+        <v>0.314</v>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0.22</v>
+        <v>0.257</v>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>0.273</v>
+        <v>0.297</v>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0.235</v>
+        <v>0.291</v>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>0.262</v>
+        <v>0.239</v>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>0.216</v>
+        <v>0.293</v>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>0.346</v>
+        <v>0.272</v>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>0.226</v>
+        <v>0.264</v>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>0.256</v>
+        <v>0.292</v>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>5.883</v>
+        <v>4.026</v>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>0.215</v>
+        <v>0.28</v>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0.268</v>
+        <v>0.276</v>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0.219</v>
+        <v>0.278</v>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0.264</v>
+        <v>0.31</v>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>0.219</v>
+        <v>0.269</v>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.27</v>
+        <v>0.249</v>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="E329" s="2" t="n">
-        <v>0.214</v>
+        <v>0.309</v>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>0.249</v>
+        <v>0.275</v>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0.217</v>
+        <v>0.251</v>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>0.211</v>
+        <v>0.292</v>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0.289</v>
+        <v>0.259</v>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>0.208</v>
+        <v>0.285</v>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>0.11</v>
+        <v>0.291</v>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0.255</v>
+        <v>0.285</v>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0.275</v>
+        <v>0.28</v>
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>0.199</v>
+        <v>0.279</v>
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>0.264</v>
+        <v>0.283</v>
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>0.221</v>
+        <v>0.281</v>
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>0.262</v>
+        <v>0.288</v>
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>2.034</v>
+        <v>2.717</v>
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="E343" s="2" t="n">
-        <v>0.216</v>
+        <v>0.254</v>
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>0.263</v>
+        <v>0.282</v>
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>0.22</v>
+        <v>0.253</v>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>0.249</v>
+        <v>0.335</v>
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>0.223</v>
+        <v>0.26</v>
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="E348" s="2" t="n">
-        <v>0.198</v>
+        <v>0.335</v>
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="E349" s="2" t="n">
-        <v>0.26</v>
+        <v>0.222</v>
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>0.216</v>
+        <v>0.293</v>
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>0.213</v>
+        <v>0.284</v>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="E353" s="2" t="n">
-        <v>0.251</v>
+        <v>0.255</v>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="E354" s="2" t="n">
-        <v>0.226</v>
+        <v>0.296</v>
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         </is>
       </c>
       <c r="E355" s="2" t="n">
-        <v>0.25</v>
+        <v>0.264</v>
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="E356" s="2" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>0.261</v>
+        <v>0.3</v>
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>0.21</v>
+        <v>0.263</v>
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="E359" s="2" t="n">
-        <v>0.254</v>
+        <v>0.246</v>
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>0.211</v>
+        <v>0.288</v>
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>0.243</v>
+        <v>0.283</v>
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>9.519</v>
+        <v>2.206</v>
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>0.283</v>
+        <v>0.295</v>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>0.23</v>
+        <v>0.288</v>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="E365" s="2" t="n">
-        <v>0.224</v>
+        <v>0.343</v>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="E366" s="2" t="n">
-        <v>0.257</v>
+        <v>0.251</v>
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="E367" s="2" t="n">
-        <v>0.223</v>
+        <v>0.32</v>
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>0.252</v>
+        <v>0.257</v>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>0.222</v>
+        <v>0.309</v>
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>0.214</v>
+        <v>0.251</v>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>0.268</v>
+        <v>0.294</v>
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>0.227</v>
+        <v>0.324</v>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>0.262</v>
+        <v>0.266</v>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>0.222</v>
+        <v>0.252</v>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>0.22</v>
+        <v>0.309</v>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>0.267</v>
+        <v>0.252</v>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>0.217</v>
+        <v>0.287</v>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>0.259</v>
+        <v>0.311</v>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>0.213</v>
+        <v>0.264</v>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>0.254</v>
+        <v>0.246</v>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="E381" s="2" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="E382" s="2" t="n">
-        <v>13.297</v>
+        <v>2.437</v>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>0.292</v>
+        <v>0.272</v>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="E384" s="2" t="n">
-        <v>0.245</v>
+        <v>0.292</v>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>0.281</v>
+        <v>0.267</v>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>0.472</v>
+        <v>0.667</v>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>0.388</v>
+        <v>0.274</v>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>0.283</v>
+        <v>0.303</v>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>0.266</v>
+        <v>0.332</v>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>0.588</v>
+        <v>0.653</v>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>0.252</v>
+        <v>0.272</v>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>0.304</v>
+        <v>0.336</v>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>0.239</v>
+        <v>0.271</v>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>0.622</v>
+        <v>0.656</v>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>0.246</v>
+        <v>0.296</v>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>0.274</v>
+        <v>0.284</v>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>0.248</v>
+        <v>0.312</v>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.623</v>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>0.229</v>
+        <v>0.308</v>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>0.302</v>
+        <v>0.24</v>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>14.691</v>
+        <v>1.922</v>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>0.125</v>
+        <v>0.211</v>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>0.158</v>
+        <v>0.181</v>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>0.115</v>
+        <v>0.16</v>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>0.174</v>
+        <v>0.2</v>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>0.119</v>
+        <v>0.205</v>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>0.108</v>
+        <v>0.17</v>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>0.168</v>
+        <v>0.23</v>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>0.13</v>
+        <v>0.161</v>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>0.126</v>
+        <v>0.231</v>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>0.177</v>
+        <v>0.157</v>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>0.121</v>
+        <v>0.2</v>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>0.156</v>
+        <v>0.191</v>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>0.117</v>
+        <v>0.188</v>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>0.168</v>
+        <v>0.193</v>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>0.115</v>
+        <v>0.19</v>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>0.173</v>
+        <v>0.188</v>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>0.155</v>
+        <v>0.208</v>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>0.184</v>
+        <v>0.19</v>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>11.503</v>
+        <v>3.379</v>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>0.218</v>
+        <v>0.184</v>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>0.184</v>
+        <v>0.224</v>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>0.165</v>
+        <v>0.197</v>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>0.21</v>
+        <v>0.254</v>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>0.168</v>
+        <v>0.198</v>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>0.213</v>
+        <v>0.241</v>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>0.168</v>
+        <v>0.27</v>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>0.212</v>
+        <v>0.22</v>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>0.173</v>
+        <v>0.201</v>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>0.164</v>
+        <v>0.253</v>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>0.206</v>
+        <v>0.169</v>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>0.178</v>
+        <v>0.236</v>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>0.198</v>
+        <v>0.231</v>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>0.167</v>
+        <v>0.198</v>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>0.211</v>
+        <v>0.233</v>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>0.18</v>
+        <v>0.225</v>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>0.164</v>
+        <v>0.213</v>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>0.21</v>
+        <v>0.236</v>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>0.17</v>
+        <v>0.219</v>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>0.217</v>
+        <v>0.198</v>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>0.182</v>
+        <v>0.256</v>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>0.237</v>
+        <v>0.208</v>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>0.201</v>
+        <v>0.248</v>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>0.209</v>
+        <v>0.234</v>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>0.162</v>
+        <v>0.232</v>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>0.166</v>
+        <v>0.239</v>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>0.215</v>
+        <v>0.171</v>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>0.169</v>
+        <v>0.242</v>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>0.198</v>
+        <v>0.228</v>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>0.177</v>
+        <v>0.201</v>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>0.209</v>
+        <v>0.236</v>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>0.166</v>
+        <v>0.218</v>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>0.167</v>
+        <v>0.24</v>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>0.207</v>
+        <v>0.222</v>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>0.194</v>
+        <v>0.204</v>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>0.208</v>
+        <v>0.242</v>
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>0.178</v>
+        <v>0.222</v>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>0.198</v>
+        <v>0.2</v>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>0.165</v>
+        <v>0.238</v>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>0.166</v>
+        <v>0.198</v>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>0.165</v>
+        <v>0.225</v>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>0.168</v>
+        <v>0.237</v>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.001</v>
+        <v>25.774</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.224</v>
+        <v>0.236</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.189</v>
+        <v>0.288</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.239</v>
+        <v>0.218</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.182</v>
+        <v>0.31</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.369</v>
+        <v>0.242</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.275</v>
+        <v>0.332</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.317</v>
+        <v>0.258</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.374</v>
+        <v>0.445</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.315</v>
+        <v>0.506</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.181</v>
+        <v>0.308</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.217</v>
+        <v>0.29</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.203</v>
+        <v>0.295</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.21</v>
+        <v>0.279</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.168</v>
+        <v>0.228</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.178</v>
+        <v>0.249</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.227</v>
+        <v>0.248</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.167</v>
+        <v>0.262</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.22</v>
+        <v>0.239</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.172</v>
+        <v>0.218</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.213</v>
+        <v>0.26</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.169</v>
+        <v>0.229</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.207</v>
+        <v>0.216</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.166</v>
+        <v>0.27</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.212</v>
+        <v>0.24</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.175</v>
+        <v>0.224</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.18</v>
+        <v>0.243</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.207</v>
+        <v>0.224</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.177</v>
+        <v>0.276</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.213</v>
+        <v>0.243</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.239</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.221</v>
+        <v>0.266</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.172</v>
+        <v>0.245</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.217</v>
+        <v>0.248</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.174</v>
+        <v>0.328</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.215</v>
+        <v>0.293</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.168</v>
+        <v>0.239</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.214</v>
+        <v>0.253</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3.46</v>
+        <v>14.577</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.258</v>
+        <v>0.325</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.378</v>
+        <v>0.577</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.222</v>
+        <v>0.349</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.276</v>
+        <v>0.337</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.224</v>
+        <v>0.269</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.253</v>
+        <v>0.258</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.211</v>
+        <v>0.231</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.255</v>
+        <v>0.278</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.209</v>
+        <v>0.266</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.246</v>
+        <v>0.307</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.222</v>
+        <v>0.292</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.253</v>
+        <v>0.297</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.225</v>
+        <v>0.303</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.216</v>
+        <v>0.27</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.255</v>
+        <v>0.218</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.216</v>
+        <v>0.265</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.252</v>
+        <v>0.259</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.226</v>
+        <v>0.312</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.289</v>
+        <v>0.268</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.292</v>
+        <v>0.25</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.227</v>
+        <v>0.287</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.21</v>
+        <v>0.276</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.251</v>
+        <v>0.254</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.216</v>
+        <v>0.291</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.266</v>
+        <v>0.271</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.211</v>
+        <v>0.266</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.257</v>
+        <v>0.303</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.229</v>
+        <v>0.277</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.25</v>
+        <v>0.218</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.215</v>
+        <v>0.294</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.248</v>
+        <v>0.282</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.22</v>
+        <v>0.252</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.258</v>
+        <v>0.297</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.214</v>
+        <v>0.285</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.254</v>
+        <v>0.248</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.212</v>
+        <v>0.261</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.256</v>
+        <v>0.276</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.211</v>
+        <v>0.263</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>3.378</v>
+        <v>5.068</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.36</v>
+        <v>0.437</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.373</v>
+        <v>0.421</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.34</v>
+        <v>0.442</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.288</v>
+        <v>0.274</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.23</v>
+        <v>0.255</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.251</v>
+        <v>0.37</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.21</v>
+        <v>0.257</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.257</v>
+        <v>0.43</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.214</v>
+        <v>0.331</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.265</v>
+        <v>0.323</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.206</v>
+        <v>0.31</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.253</v>
+        <v>0.316</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>0.219</v>
+        <v>0.302</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.249</v>
+        <v>0.296</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0.21</v>
+        <v>0.294</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.215</v>
+        <v>0.303</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.242</v>
+        <v>0.292</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.209</v>
+        <v>0.301</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.242</v>
+        <v>0.311</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.21</v>
+        <v>0.304</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.247</v>
+        <v>0.328</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.216</v>
+        <v>0.293</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.249</v>
+        <v>0.268</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.208</v>
+        <v>0.303</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.198</v>
+        <v>0.274</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.275</v>
+        <v>0.292</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.226</v>
+        <v>0.534</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.261</v>
+        <v>0.305</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>5.556</v>
+        <v>4.609</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.294</v>
+        <v>0.382</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.251</v>
+        <v>0.648</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.242</v>
+        <v>0.466</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.112</v>
+        <v>0.331</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.262</v>
+        <v>0.242</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.271</v>
+        <v>0.232</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.216</v>
+        <v>0.34</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.252</v>
+        <v>0.336</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.219</v>
+        <v>0.32</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.26</v>
+        <v>0.375</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.216</v>
+        <v>0.401</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.248</v>
+        <v>0.284</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.218</v>
+        <v>0.43</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.216</v>
+        <v>0.362</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.26</v>
+        <v>0.232</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.214</v>
+        <v>0.334</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.243</v>
+        <v>0.328</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.213</v>
+        <v>0.315</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.255</v>
+        <v>0.382</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.212</v>
+        <v>0.322</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.254</v>
+        <v>0.285</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.223</v>
+        <v>0.256</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.255</v>
+        <v>0.295</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.222</v>
+        <v>0.279</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.29</v>
+        <v>0.256</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.211</v>
+        <v>0.298</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.262</v>
+        <v>0.275</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.208</v>
+        <v>0.258</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.263</v>
+        <v>0.314</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.216</v>
+        <v>0.296</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.281</v>
+        <v>0.274</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.219</v>
+        <v>0.304</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.321</v>
+        <v>0.277</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.248</v>
+        <v>0.252</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.222</v>
+        <v>0.299</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.224</v>
+        <v>0.272</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.252</v>
+        <v>0.26</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.22</v>
+        <v>0.303</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.262</v>
+        <v>0.273</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.24</v>
+        <v>0.257</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.261</v>
+        <v>0.308</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.212</v>
+        <v>0.28</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.267</v>
+        <v>0.265</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>0.217</v>
+        <v>0.308</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.252</v>
+        <v>0.28</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.219</v>
+        <v>0.275</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.249</v>
+        <v>0.318</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.233</v>
+        <v>0.274</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.265</v>
+        <v>0.276</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>10.929</v>
+        <v>4.643</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.298</v>
+        <v>0.336</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.325</v>
+        <v>0.312</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.219</v>
+        <v>0.301</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>0.261</v>
+        <v>0.31</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>0.217</v>
+        <v>0.282</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.26</v>
+        <v>0.227</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.224</v>
+        <v>0.282</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.266</v>
+        <v>0.326</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.195</v>
+        <v>0.278</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.258</v>
+        <v>0.306</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.214</v>
+        <v>0.251</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.267</v>
+        <v>0.304</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.196</v>
+        <v>0.266</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.245</v>
+        <v>0.318</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.211</v>
+        <v>0.257</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.267</v>
+        <v>0.307</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.224</v>
+        <v>0.254</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.288</v>
+        <v>0.307</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.222</v>
+        <v>0.252</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.284</v>
+        <v>0.305</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.217</v>
+        <v>0.266</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.26</v>
+        <v>0.304</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.225</v>
+        <v>0.267</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.272</v>
+        <v>0.299</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.223</v>
+        <v>0.25</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.292</v>
+        <v>0.317</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.256</v>
+        <v>0.252</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.244</v>
+        <v>0.304</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.211</v>
+        <v>0.251</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.269</v>
+        <v>0.352</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.229</v>
+        <v>0.259</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.263</v>
+        <v>0.304</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.22</v>
+        <v>0.248</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.268</v>
+        <v>0.299</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.216</v>
+        <v>0.248</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.244</v>
+        <v>0.3</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.217</v>
+        <v>0.234</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.257</v>
+        <v>0.311</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.217</v>
+        <v>0.265</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.286</v>
+        <v>0.305</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.224</v>
+        <v>0.266</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.273</v>
+        <v>0.299</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.22</v>
+        <v>0.246</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.249</v>
+        <v>0.309</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>0.22</v>
+        <v>0.246</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.258</v>
+        <v>0.3</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.219</v>
+        <v>0.278</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.31</v>
+        <v>0.308</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>3.164</v>
+        <v>3.579</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.265</v>
+        <v>0.293</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>0.25</v>
+        <v>0.303</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>0.221</v>
+        <v>0.287</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0.267</v>
+        <v>0.331</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0.234</v>
+        <v>0.267</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>0.117</v>
+        <v>0.257</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0.316</v>
+        <v>0.337</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>0.259</v>
+        <v>0.214</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0.227</v>
+        <v>0.302</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>0.29</v>
+        <v>0.293</v>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>0.224</v>
+        <v>0.311</v>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.233</v>
+        <v>0.319</v>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0.251</v>
+        <v>0.268</v>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>0.215</v>
+        <v>0.314</v>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.239</v>
+        <v>0.306</v>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>0.251</v>
+        <v>0.32</v>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>0.234</v>
+        <v>0.325</v>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.267</v>
+        <v>0.291</v>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>0.22</v>
+        <v>0.301</v>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0.237</v>
+        <v>0.335</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>0.215</v>
+        <v>0.318</v>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.261</v>
+        <v>0.309</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>0.222</v>
+        <v>0.322</v>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.277</v>
+        <v>0.322</v>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>0.22</v>
+        <v>0.303</v>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.133</v>
+        <v>0.369</v>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.363</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.253</v>
+        <v>0.294</v>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.226</v>
+        <v>0.292</v>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         </is>
       </c>
       <c r="E243" s="2" t="n">
-        <v>0.126</v>
+        <v>0.285</v>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>0.285</v>
+        <v>0.284</v>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="E245" s="2" t="n">
-        <v>0.26</v>
+        <v>0.291</v>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         </is>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.235</v>
+        <v>0.292</v>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>0.249</v>
+        <v>0.284</v>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.213</v>
+        <v>0.282</v>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         </is>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.2</v>
+        <v>0.283</v>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         </is>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.246</v>
+        <v>0.305</v>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="E252" s="2" t="n">
-        <v>0.216</v>
+        <v>0.296</v>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         </is>
       </c>
       <c r="E253" s="2" t="n">
-        <v>0.281</v>
+        <v>0.286</v>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0.255</v>
+        <v>0.228</v>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         </is>
       </c>
       <c r="E255" s="2" t="n">
-        <v>0.257</v>
+        <v>0.313</v>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         </is>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.246</v>
+        <v>0.257</v>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>0.256</v>
+        <v>0.307</v>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.227</v>
+        <v>0.293</v>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.198</v>
+        <v>0.257</v>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.233</v>
+        <v>0.299</v>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         </is>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.226</v>
+        <v>0.282</v>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         </is>
       </c>
       <c r="E262" s="2" t="n">
-        <v>3.259</v>
+        <v>2.493</v>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.268</v>
+        <v>0.303</v>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0.307</v>
+        <v>0.291</v>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0.216</v>
+        <v>0.314</v>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0.263</v>
+        <v>0.266</v>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0.222</v>
+        <v>0.284</v>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0.286</v>
+        <v>0.424</v>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.229</v>
+        <v>0.25</v>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.269</v>
+        <v>0.376</v>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.224</v>
+        <v>0.274</v>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.257</v>
+        <v>0.364</v>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.219</v>
+        <v>0.317</v>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.222</v>
+        <v>0.297</v>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.28</v>
+        <v>0.272</v>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>0.219</v>
+        <v>0.25</v>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0.29</v>
+        <v>0.292</v>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>0.222</v>
+        <v>0.272</v>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.251</v>
+        <v>0.249</v>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.217</v>
+        <v>0.313</v>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>0.255</v>
+        <v>0.275</v>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>0.218</v>
+        <v>0.248</v>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>0.271</v>
+        <v>0.298</v>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.201</v>
+        <v>0.334</v>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>0.263</v>
+        <v>0.309</v>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.219</v>
+        <v>0.316</v>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>0.199</v>
+        <v>0.293</v>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>0.252</v>
+        <v>0.269</v>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>0.217</v>
+        <v>0.3</v>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>0.217</v>
+        <v>0.274</v>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>0.26</v>
+        <v>0.255</v>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.213</v>
+        <v>0.342</v>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>0.263</v>
+        <v>0.305</v>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         </is>
       </c>
       <c r="E295" s="2" t="n">
-        <v>0.223</v>
+        <v>0.3</v>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>0.288</v>
+        <v>0.303</v>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>0.282</v>
+        <v>0.296</v>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>0.238</v>
+        <v>0.307</v>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>0.215</v>
+        <v>0.298</v>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.258</v>
+        <v>0.318</v>
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.195</v>
+        <v>0.265</v>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>1.322</v>
+        <v>2.101</v>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0.261</v>
+        <v>0.294</v>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0.277</v>
+        <v>0.308</v>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="E305" s="2" t="n">
-        <v>0.217</v>
+        <v>0.268</v>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>0.257</v>
+        <v>0.254</v>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         </is>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.198</v>
+        <v>0.293</v>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0.26</v>
+        <v>0.291</v>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         </is>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0.285</v>
+        <v>0.289</v>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0.242</v>
+        <v>0.275</v>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>0.24</v>
+        <v>0.254</v>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>0.27</v>
+        <v>0.314</v>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0.22</v>
+        <v>0.257</v>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>0.273</v>
+        <v>0.297</v>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0.235</v>
+        <v>0.291</v>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>0.262</v>
+        <v>0.239</v>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>0.216</v>
+        <v>0.293</v>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>0.346</v>
+        <v>0.272</v>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>0.226</v>
+        <v>0.264</v>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>0.256</v>
+        <v>0.292</v>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>5.883</v>
+        <v>4.026</v>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>0.215</v>
+        <v>0.28</v>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0.268</v>
+        <v>0.276</v>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0.219</v>
+        <v>0.278</v>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0.264</v>
+        <v>0.31</v>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>0.219</v>
+        <v>0.269</v>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.27</v>
+        <v>0.249</v>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="E329" s="2" t="n">
-        <v>0.214</v>
+        <v>0.309</v>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>0.249</v>
+        <v>0.275</v>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0.217</v>
+        <v>0.251</v>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>0.211</v>
+        <v>0.292</v>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0.289</v>
+        <v>0.259</v>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>0.208</v>
+        <v>0.285</v>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>0.11</v>
+        <v>0.291</v>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0.255</v>
+        <v>0.285</v>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0.275</v>
+        <v>0.28</v>
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>0.199</v>
+        <v>0.279</v>
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>0.264</v>
+        <v>0.283</v>
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>0.221</v>
+        <v>0.281</v>
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>0.262</v>
+        <v>0.288</v>
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>2.034</v>
+        <v>2.717</v>
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="E343" s="2" t="n">
-        <v>0.216</v>
+        <v>0.254</v>
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>0.263</v>
+        <v>0.282</v>
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>0.22</v>
+        <v>0.253</v>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>0.249</v>
+        <v>0.335</v>
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>0.223</v>
+        <v>0.26</v>
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="E348" s="2" t="n">
-        <v>0.198</v>
+        <v>0.335</v>
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="E349" s="2" t="n">
-        <v>0.26</v>
+        <v>0.222</v>
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>0.216</v>
+        <v>0.293</v>
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>0.213</v>
+        <v>0.284</v>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="E353" s="2" t="n">
-        <v>0.251</v>
+        <v>0.255</v>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         </is>
       </c>
       <c r="E354" s="2" t="n">
-        <v>0.226</v>
+        <v>0.296</v>
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         </is>
       </c>
       <c r="E355" s="2" t="n">
-        <v>0.25</v>
+        <v>0.264</v>
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="E356" s="2" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>0.261</v>
+        <v>0.3</v>
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>0.21</v>
+        <v>0.263</v>
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="E359" s="2" t="n">
-        <v>0.254</v>
+        <v>0.246</v>
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>0.211</v>
+        <v>0.288</v>
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>0.243</v>
+        <v>0.283</v>
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>9.519</v>
+        <v>2.206</v>
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>0.283</v>
+        <v>0.295</v>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>0.23</v>
+        <v>0.288</v>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="E365" s="2" t="n">
-        <v>0.224</v>
+        <v>0.343</v>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         </is>
       </c>
       <c r="E366" s="2" t="n">
-        <v>0.257</v>
+        <v>0.251</v>
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         </is>
       </c>
       <c r="E367" s="2" t="n">
-        <v>0.223</v>
+        <v>0.32</v>
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>0.252</v>
+        <v>0.257</v>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>0.222</v>
+        <v>0.309</v>
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>0.214</v>
+        <v>0.251</v>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>0.268</v>
+        <v>0.294</v>
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>0.227</v>
+        <v>0.324</v>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>0.262</v>
+        <v>0.266</v>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>0.222</v>
+        <v>0.252</v>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>0.22</v>
+        <v>0.309</v>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>0.267</v>
+        <v>0.252</v>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>0.217</v>
+        <v>0.287</v>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>0.259</v>
+        <v>0.311</v>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>0.213</v>
+        <v>0.264</v>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>0.254</v>
+        <v>0.246</v>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         </is>
       </c>
       <c r="E381" s="2" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="E382" s="2" t="n">
-        <v>13.297</v>
+        <v>2.437</v>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>0.292</v>
+        <v>0.272</v>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         </is>
       </c>
       <c r="E384" s="2" t="n">
-        <v>0.245</v>
+        <v>0.292</v>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>0.281</v>
+        <v>0.267</v>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>0.472</v>
+        <v>0.667</v>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>0.388</v>
+        <v>0.274</v>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>0.283</v>
+        <v>0.303</v>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>0.266</v>
+        <v>0.332</v>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>0.588</v>
+        <v>0.653</v>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>0.252</v>
+        <v>0.272</v>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>0.304</v>
+        <v>0.336</v>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>0.239</v>
+        <v>0.271</v>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>0.622</v>
+        <v>0.656</v>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>0.246</v>
+        <v>0.296</v>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>0.274</v>
+        <v>0.284</v>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>0.248</v>
+        <v>0.312</v>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.623</v>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>0.229</v>
+        <v>0.308</v>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>0.302</v>
+        <v>0.24</v>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>14.691</v>
+        <v>1.922</v>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>0.125</v>
+        <v>0.211</v>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>0.158</v>
+        <v>0.181</v>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>0.115</v>
+        <v>0.16</v>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>0.174</v>
+        <v>0.2</v>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>0.119</v>
+        <v>0.205</v>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>0.108</v>
+        <v>0.17</v>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>0.168</v>
+        <v>0.23</v>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>0.13</v>
+        <v>0.161</v>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>0.126</v>
+        <v>0.231</v>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>0.177</v>
+        <v>0.157</v>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>0.121</v>
+        <v>0.2</v>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>0.156</v>
+        <v>0.191</v>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>0.117</v>
+        <v>0.188</v>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>0.168</v>
+        <v>0.193</v>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>0.115</v>
+        <v>0.19</v>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>0.173</v>
+        <v>0.188</v>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>0.155</v>
+        <v>0.208</v>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>0.184</v>
+        <v>0.19</v>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>11.503</v>
+        <v>3.379</v>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>0.218</v>
+        <v>0.184</v>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>0.184</v>
+        <v>0.224</v>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>0.165</v>
+        <v>0.197</v>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>0.21</v>
+        <v>0.254</v>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>0.168</v>
+        <v>0.198</v>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>0.213</v>
+        <v>0.241</v>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>0.168</v>
+        <v>0.27</v>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>0.212</v>
+        <v>0.22</v>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>0.173</v>
+        <v>0.201</v>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>0.164</v>
+        <v>0.253</v>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>0.206</v>
+        <v>0.169</v>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>0.178</v>
+        <v>0.236</v>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>0.198</v>
+        <v>0.231</v>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>0.167</v>
+        <v>0.198</v>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>0.211</v>
+        <v>0.233</v>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>0.18</v>
+        <v>0.225</v>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>0.164</v>
+        <v>0.213</v>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>0.21</v>
+        <v>0.236</v>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>0.17</v>
+        <v>0.219</v>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>0.217</v>
+        <v>0.198</v>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>0.182</v>
+        <v>0.256</v>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>0.237</v>
+        <v>0.208</v>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>0.201</v>
+        <v>0.248</v>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>0.209</v>
+        <v>0.234</v>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>0.162</v>
+        <v>0.232</v>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>0.166</v>
+        <v>0.239</v>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>0.215</v>
+        <v>0.171</v>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>0.169</v>
+        <v>0.242</v>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>0.198</v>
+        <v>0.228</v>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>0.177</v>
+        <v>0.201</v>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>0.209</v>
+        <v>0.236</v>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>0.166</v>
+        <v>0.218</v>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>0.167</v>
+        <v>0.24</v>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>0.207</v>
+        <v>0.222</v>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>0.194</v>
+        <v>0.204</v>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>0.208</v>
+        <v>0.242</v>
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>0.178</v>
+        <v>0.222</v>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>0.198</v>
+        <v>0.2</v>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>0.165</v>
+        <v>0.238</v>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>0.166</v>
+        <v>0.198</v>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>0.165</v>
+        <v>0.225</v>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>0.168</v>
+        <v>0.237</v>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>244.12s</t>
+          <t>250.04s</t>
         </is>
       </c>
     </row>
